--- a/xlsx/sc-endgame.xlsx
+++ b/xlsx/sc-endgame.xlsx
@@ -3291,7 +3291,7 @@
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3396,6 +3396,11 @@
           <t>Aiolos | Attitude | KnockOut | Octagon | Backrooms | Attitude | Aiolos | KnockOut | Octagon</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dPPWOFu0PuI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3442,6 +3447,11 @@
           <t>KnockOut | Attitude | Backrooms | Aiolos | Octagon | Attitude | Backrooms | KnockOut | Octagon</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fpRTsM4wXPI</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3488,6 +3498,11 @@
           <t>Octagon | Backrooms | Attitude | Aiolos | KnockOut | Octagon | Attitude | Backrooms | KnockOut</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fzRfw30LbdE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3534,6 +3549,11 @@
           <t>Colorless Fate | Octagon | Aiolos | Backrooms | KnockOut | Backrooms | Octagon | Colorless Fate | Aiolos</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5gx1JNs1pYY</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3580,6 +3600,11 @@
           <t>Colorless Fate | Octagon | Aiolos | KnockOut | Backrooms | Aiolos | Octagon | KnockOut | Backrooms</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kqcV85ZsIEg</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3626,6 +3651,11 @@
           <t>Octagon | Attitude | KnockOut | Aiolos | Odyssey | Attitude | Odyssey | Octagon | KnockOut</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_BQJTqDEoCc</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3672,6 +3702,11 @@
           <t>Neo Sylphid | Pole Star | Attitude | Octagon | KnockOut | Pole Star | Neo Sylphid | Octagon | Attitude</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=N1BuzYXwHDc</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3718,6 +3753,11 @@
           <t>Neo Sylphid | MatchPoint | Pole Star | KnockOut | Octagon | Pole Star | MatchPoint | KnockOut | Octagon</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tbBmwpPgiDI</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3764,6 +3804,11 @@
           <t>MatchPoint | Attitude | Octagon | Neo Sylphid | KnockOut | Attitude | MatchPoint | KnockOut | Octagon</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RjK9Y4xTxZg</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3810,6 +3855,11 @@
           <t>Jane doe | Pole Star | Octagon | KnockOut | Neo Sylphid | Jane doe | Pole Star | Neo Sylphid | KnockOut</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xqVOOt7re-E</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3856,6 +3906,11 @@
           <t>Pole Star | MatchPoint | Octagon | KnockOut | Neo Sylphid | Pole Star | MatchPoint | Octagon | KnockOut</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wQ6rgaR3BkI</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3902,6 +3957,11 @@
           <t>Attitude | MatchPoint | Octagon | Neo Sylphid | KnockOut | MatchPoint | Attitude | Octagon | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FWyc2E1vCcc</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3948,6 +4008,11 @@
           <t>Pole Star | Neo Sylphid | MatchPoint | Octagon | KnockOut | Pole Star | MatchPoint | Neo Sylphid | KnockOut</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XDPZGsdRC58</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3994,6 +4059,11 @@
           <t>Attitude | Jane doe | Octagon | KnockOut | Neo Sylphid | Jane doe | Attitude | Octagon | KnockOut</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ddmsudtqzLM</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4040,6 +4110,11 @@
           <t>Octagon | Neo Sylphid | Jane doe | KnockOut | Pole Star | Neo Sylphid | Jane doe | Octagon | Pole Star</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FZLPkgrwYgM</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4086,6 +4161,11 @@
           <t>Jane doe | Neo Sylphid | Attitude | Octagon | KnockOut | Attitude | Jane doe | Octagon | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=j8ERHqnRLzs</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4132,6 +4212,11 @@
           <t>Pole Star | Neo Sylphid | KnockOut | Octagon | Attitude | Pole Star | Neo Sylphid | Octagon | Attitude</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jSC4gVI8yVQ</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4178,6 +4263,11 @@
           <t>MatchPoint | Pole Star | KnockOut | Jane doe | Octagon | Pole Star | MatchPoint | KnockOut | Jane doe</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2Jw_-9Zq0m8</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4224,6 +4314,11 @@
           <t>KnockOut | Jane doe | Octagon | Neo Sylphid | Attitude | Jane doe | Octagon | Attitude | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FzubbPC85UQ</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4270,6 +4365,11 @@
           <t>Octagon | MatchPoint | Jane doe | Neo Sylphid | Attitude | Octagon | MatchPoint | Neo Sylphid | Attitude</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OeEN_NBrFfw</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4316,6 +4416,11 @@
           <t>Attitude | Jane doe | Neo Sylphid | KnockOut | Octagon | Jane doe | Attitude | Octagon | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-M7A0CO-P9E</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4362,6 +4467,11 @@
           <t>Octagon | KnockOut | Pole Star | MatchPoint | Attitude | Pole Star | Attitude | Octagon | MatchPoint</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3-VU2WUeD0c</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4408,6 +4518,11 @@
           <t>Octagon | Pole Star | Neo Sylphid | Jane doe | KnockOut | Jane doe | Octagon | Neo Sylphid | KnockOut</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lSk3eQDPD0Y</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4454,6 +4569,11 @@
           <t>KnockOut | Octagon | Pole Star | Jane doe | Attitude | KnockOut | Pole Star | Octagon | Jane doe</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aTBX_EjzVSY</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4500,6 +4620,11 @@
           <t>Neo Sylphid | Pole Star | Jane doe | Octagon | KnockOut | Pole Star | Jane doe | Neo Sylphid | Octagon</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WRFzyPuZvT4</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4546,6 +4671,11 @@
           <t>Attitude | Pole Star | Octagon | Neo Sylphid | MatchPoint | Neo Sylphid | Octagon | MatchPoint | Attitude</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zkvsO4wm66A</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4592,6 +4722,11 @@
           <t>MatchPoint | Neo Sylphid | Pole Star | KnockOut | Octagon | Pole Star | MatchPoint | Neo Sylphid | Octagon</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QK9ZCSgOV08</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4638,6 +4773,11 @@
           <t>Radeon | KnockOut | Metropolis | Dominator | Litmus | Radeon | KnockOut | Metropolis | Dominator</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bGSVSbPHjuk</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4684,6 +4824,11 @@
           <t>Metropolis | Radeon | Dominator | KnockOut | Litmus | Litmus | Dominator | Metropolis | KnockOut</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_bZ962ocE0c</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4730,6 +4875,11 @@
           <t>Pole Star | Metropolis | Litmus | Radeon | KnockOut | Pole Star | Metropolis | Radeon | Litmus</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6EudlvRvFcU</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4776,6 +4926,11 @@
           <t>Pole Star | Metropolis | Radeon | Dominator | Roaring Currents | Pole Star | Radeon | Metropolis | Dominator</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZRCvqkECXSY</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4822,6 +4977,11 @@
           <t>Metropolis | Radeon | Litmus | Pole Star | KnockOut | Litmus | Metropolis | KnockOut | Pole Star</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WbaKn0uIyYU</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4868,6 +5028,11 @@
           <t>Pole Star | Radeon | KnockOut | Metropolis | Dominator | Pole Star | Dominator | KnockOut | Metropolis</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wA4aB88gS2Y</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4914,6 +5079,11 @@
           <t>Radeon | Litmus | Metropolis | KnockOut | Dominator | Litmus | Metropolis | Dominator | Radeon</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bRTktyeAlag</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4960,6 +5130,11 @@
           <t>Pole Star | KnockOut | Radeon | Dominator | Litmus | Dominator | Litmus | Pole Star | Radeon</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=jYZj_tSqWEw</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5006,6 +5181,11 @@
           <t>Metropolis | Dominator | Radeon | KnockOut | Litmus | Dominator | Litmus | Metropolis | Radeon</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2p99vl6EOm0</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5052,6 +5232,11 @@
           <t>Radeon | Metropolis | Dominator | KnockOut | Litmus | Radeon | Dominator | Metropolis | KnockOut</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vNX8fqKQoX8</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5098,6 +5283,11 @@
           <t>Pole Star | Dominator | Litmus | Radeon | KnockOut | Litmus | Pole Star | KnockOut | Radeon</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=H-D-995rvuw</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5144,6 +5334,11 @@
           <t>Dominator | Metropolis | Roaring Currents | Pole Star | Radeon | Roaring Currents | Metropolis | Dominator | Pole Star</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lgHuir_H1FQ</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5190,6 +5385,11 @@
           <t>Dominator | Radeon | KnockOut | Litmus | Metropolis | Dominator | Metropolis | Radeon | Litmus</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ln9U43sQsF8</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5236,6 +5436,11 @@
           <t>Radeon | Pole Star | Dominator | Metropolis | KnockOut | Pole Star | Dominator | Metropolis | Radeon</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8x-olAMLhlg</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5282,6 +5487,11 @@
           <t>Pole Star | Metropolis | Dominator | Radeon | KnockOut | Pole Star | Metropolis | Dominator | Radeon</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NLDKF5-z41U</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5328,6 +5538,11 @@
           <t>Radeon | Dominator | Metropolis | Pole Star | Litmus | Radeon | Dominator | Litmus | Metropolis</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RjkuQhk3Ekw</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5374,6 +5589,11 @@
           <t>Radeon | Metropolis | Pole Star | KnockOut | Dominator | Metropolis | Pole Star | KnockOut | Dominator</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ax83TDHl3JE</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5420,6 +5640,11 @@
           <t>Radeon | Roaring Currents | KnockOut | Metropolis | Dominator | Metropolis | Radeon | Dominator | KnockOut</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nlftc9uKYeg</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5466,6 +5691,11 @@
           <t>Pole Star | KnockOut | Metropolis | Dominator | Litmus | Pole Star | Dominator | Metropolis | KnockOut</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W-UGrIkC0wQ</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5512,6 +5742,11 @@
           <t>Litmus | Metropolis | Dominator | Radeon | KnockOut | Metropolis | Dominator | Radeon | Litmus</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QF0coUa4nAw</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5558,6 +5793,11 @@
           <t>Radeon | Pole Star | Dominator | KnockOut | Metropolis | Pole Star | Dominator | KnockOut | Radeon</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=v5xgIZm_hPE</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5604,6 +5844,11 @@
           <t>Pole Star | Radeon | KnockOut | Dominator | Litmus | Dominator | Pole Star | Radeon | KnockOut</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Aptw0Qpgnks</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5650,6 +5895,11 @@
           <t>Metropolis | Radeon | Litmus | Dominator | KnockOut | Dominator | Litmus | Radeon | Metropolis</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UtdCzIL_lZU</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5696,6 +5946,11 @@
           <t>KnockOut | Radeon | Pole Star | Dominator | Metropolis | KnockOut | Pole Star | Dominator | Radeon</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XF9BB_Rsfp8</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5742,6 +5997,11 @@
           <t>Pole Star | Metropolis | Litmus | Radeon | Dominator | Metropolis | Pole Star | Litmus | Radeon</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vWEXbrALqcI</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5788,6 +6048,11 @@
           <t>Dominator | Radeon | déjà vu | Metropolis | Pole Star | déjà vu | Metropolis | Radeon | Pole Star</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wuKJiBKFUJw</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5834,6 +6099,11 @@
           <t>Metropolis | Pole Star | Radeon | DeathValley | Dominator | Pole Star | DeathValley | Metropolis | Dominator</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AgU2jkzTYXE</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5880,6 +6150,11 @@
           <t>déjà vu | Radeon | Eclipse | Dominator | Metropolis | Radeon | déjà vu | Metropolis | Dominator</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-c55GkjdPLY</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5926,6 +6201,11 @@
           <t>Dominator | Eclipse | Radeon | Pole Star | Metropolis | Eclipse | Metropolis | Dominator | Pole Star</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2jBsZPG9DkA</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5972,6 +6252,11 @@
           <t>déjà vu | Radeon | Eclipse | Dominator | Metropolis | Eclipse | déjà vu | Radeon | Metropolis</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lhadRpUwEdo</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6018,6 +6303,11 @@
           <t>Dominator | Radeon | Eclipse | Metropolis | Pole Star | Eclipse | Dominator | Radeon | Pole Star</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0gtlR-4jUOk</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6064,6 +6354,11 @@
           <t>Pole Star | Eclipse | déjà vu | Dominator | Radeon | Pole Star | Eclipse | déjà vu | Dominator</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QIqr6uTNmYA</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6110,6 +6405,11 @@
           <t>Dominator | Metropolis | Eclipse | déjà vu | Pole Star | Dominator | Eclipse | Metropolis | déjà vu</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RvTwS5HmmKQ</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6156,6 +6456,11 @@
           <t>Eclipse | déjà vu | Pole Star | Dominator | Radeon | Pole Star | Eclipse | déjà vu | Dominator</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iY1uYMs5Y5g</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6202,6 +6507,11 @@
           <t>Radeon | Metropolis | déjà vu | Eclipse | Dominator | Metropolis | Eclipse | Radeon | Dominator</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vx4Zl3KiKYE</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6248,6 +6558,11 @@
           <t>Pole Star | Dominator | déjà vu | Radeon | Eclipse | Eclipse | Dominator | Pole Star | déjà vu</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SUAjNu3bdrs</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6294,6 +6609,11 @@
           <t>Pole Star | Radeon | déjà vu | Metropolis | Eclipse | Pole Star | Radeon | déjà vu | Metropolis</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=3-BPnruT10c</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6340,6 +6660,11 @@
           <t>Eclipse | déjà vu | Metropolis | Radeon | Pole Star | Eclipse | déjà vu | Metropolis | Radeon</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IShXFcBSYH4</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6386,6 +6711,11 @@
           <t>Pole Star | Radeon | déjà vu | Eclipse | Metropolis | Pole Star | déjà vu | Radeon | Metropolis</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W0bV2uRdPsw</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6432,6 +6762,11 @@
           <t>Pole Star | Radeon | déjà vu | Eclipse | Dominator | Radeon | Eclipse | déjà vu | Pole Star</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1KIy_LbLZzU</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6478,6 +6813,11 @@
           <t>déjà vu | Radeon | Dominator | Pole Star | Eclipse | Radeon | déjà vu | Pole Star | Eclipse</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-26uOXx3wno</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6524,6 +6864,11 @@
           <t>Eclipse | Radeon | déjà vu | Pole Star | Dominator | déjà vu | Pole Star | Eclipse | Radeon</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kb0WpzmkJfA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6570,6 +6915,11 @@
           <t>Metropolis | Radeon | Dominator | Pole Star | Eclipse | Eclipse | Dominator | Radeon | Metropolis</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6NeJx2G2pD8</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6616,6 +6966,11 @@
           <t>Radeon | Pole Star | Eclipse | Metropolis | Dominator | Radeon | Dominator | Eclipse | Pole Star</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Y22OHeX2gZ0</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6662,6 +7017,11 @@
           <t>Eclipse | Radeon | Pole Star | Metropolis | Dominator | Radeon | Eclipse | Pole Star | Dominator</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LhcwPPVZzBw</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6708,6 +7068,11 @@
           <t>déjà vu | Metropolis | Pole Star | Radeon | Dominator | Radeon | Metropolis | Pole Star | déjà vu</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yepShRxCKg0</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6754,6 +7119,11 @@
           <t>Eclipse | déjà vu | Dominator | Pole Star | Radeon | Eclipse | Dominator | déjà vu | Pole Star</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EhKEpfwhlrw</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6800,6 +7170,11 @@
           <t>Pantheon | Radeon | déjà vu | Dominator | Kick Back | Radeon | Pantheon | déjà vu | Kick Back</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_7dIXaQF0Rs</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6846,6 +7221,11 @@
           <t>déjà vu | Pantheon | Dominator | Radeon | Kick Back | Kick Back | Pantheon | Dominator | déjà vu</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pOgRnzxE-b0</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6892,6 +7272,11 @@
           <t>Kick Back | déjà vu | Dominator | Radeon | Montyhall SE | Kick Back | déjà vu | Radeon | Montyhall SE</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C1IOmrqsXCs</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6938,6 +7323,11 @@
           <t>Kick Back | Radeon | Pantheon | Dominator | déjà vu | Kick Back | Pantheon | Radeon | déjà vu</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Eu3FNgh3ias</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6984,6 +7374,11 @@
           <t>Kick Back | Pantheon | Dominator | Radeon | déjà vu | Dominator | déjà vu | Kick Back | Radeon</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8M4n2egMT4I</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7030,6 +7425,11 @@
           <t>Minstrel | déjà vu | Montyhall SE | Dominator | Pantheon | Minstrel | déjà vu | Dominator | Pantheon</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xaKlSgrHzX4</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7076,6 +7476,11 @@
           <t>Kick Back | Pantheon | Montyhall SE | déjà vu | Dominator | Pantheon | Montyhall SE | déjà vu | Kick Back</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6Y0YaB49OWI</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7122,6 +7527,11 @@
           <t>Radeon | Kick Back | Montyhall SE | déjà vu | Minstrel | Radeon | déjà vu | Montyhall SE | Kick Back</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gJUpMaGqAtU</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7168,6 +7578,11 @@
           <t>Pantheon | Montyhall SE | déjà vu | Dominator | Kick Back | Dominator | Pantheon | Kick Back | déjà vu</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TwX8wCmqb4s</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7214,6 +7629,11 @@
           <t>Radeon | Kick Back | déjà vu | Dominator | Pantheon | déjà vu | Dominator | Kick Back | Pantheon</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=psCVQBPW1iw</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7260,6 +7680,11 @@
           <t>Montyhall SE | Kick Back | Dominator | déjà vu | Radeon | Radeon | déjà vu | Kick Back | Montyhall SE</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RCe8tHhl8VE</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7306,6 +7731,11 @@
           <t>Radeon | Minstrel | Pantheon | Dominator | Kick Back | Minstrel | Pantheon | Dominator | Kick Back</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RsaSFe2a7GY</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7352,6 +7782,11 @@
           <t>Dominator | Radeon | Montyhall SE | déjà vu | Kick Back | Dominator | Montyhall SE | Radeon | déjà vu</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aB6QmNFQnlc</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7398,6 +7833,11 @@
           <t>Radeon | Citadel | Neo Dark Origin | Retro | Apocalypse | Citadel | Neo Dark Origin | Retro | Radeon</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g-8eRy44L5M</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7444,6 +7884,11 @@
           <t>BlitzY | Apocalypse | Neo Dark Origin | Retro | Radeon | Apocalypse | BlitzY | Radeon | Retro</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iC6eNFNGpYQ</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7490,6 +7935,11 @@
           <t>Citadel | Retro | Apocalypse | Radeon | BlitzY | Apocalypse | Radeon | Retro | BlitzY</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gKNcCPZlkwM</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7536,6 +7986,11 @@
           <t>BlitzY | Neo Dark Origin | Apocalypse | Retro | Citadel | BlitzY | Apocalypse | Neo Dark Origin | Citadel</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=cFzkVr1p_zw</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7582,6 +8037,11 @@
           <t>Retro | Apocalypse | BlitzY | Troy | Radeon | Troy | Apocalypse | BlitzY | Retro</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zETRWE5S8R4</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7628,6 +8088,11 @@
           <t>Citadel | BlitzY | Retro | Apocalypse | Neo Dark Origin | BlitzY | Apocalypse | Neo Dark Origin | Retro</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-G8K6lezXwo</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7674,6 +8139,11 @@
           <t>Citadel | Neo Dark Origin | Retro | Apocalypse | BlitzY | Citadel | Retro | Neo Dark Origin | BlitzY</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TJR3dG0mRys</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7720,6 +8190,11 @@
           <t>Citadel | Apocalypse | Retro | BlitzY | Troy | Citadel | Retro | Apocalypse | BlitzY</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=a1CgHqbkCWQ</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7766,6 +8241,11 @@
           <t>Neo Dark Origin | Radeon | Apocalypse | Citadel | Troy | Radeon | Citadel | Troy | Apocalypse</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wSAro_rx0RY</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7812,6 +8292,11 @@
           <t>BlitzY | Citadel | Retro | Apocalypse | Neo Dark Origin | Citadel | BlitzY | Retro | Apocalypse</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=drSEL6aVt3o</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7858,6 +8343,11 @@
           <t>Neo Dark Origin | Retro | Radeon | Apocalypse | Citadel | Neo Dark Origin | Retro | Apocalypse | Citadel</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Aj8L7NoVAI8</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7904,6 +8394,11 @@
           <t>Citadel | BlitzY | Apocalypse | Retro | Neo Dark Origin | Citadel | Apocalypse | BlitzY | Retro</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QkXykyZVEVs</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7950,6 +8445,11 @@
           <t>Radeon | Retro | BlitzY | Apocalypse | Neo Dark Origin | BlitzY | Retro | Radeon | Apocalypse</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dAKgdPyV6BQ</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7996,6 +8496,11 @@
           <t>Apocalypse | Retro | Radeon | Neo Dark Origin | BlitzY | Retro | Apocalypse | Neo Dark Origin | BlitzY</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IbxRBD6ljiA</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8042,6 +8547,11 @@
           <t>Radeon | Citadel | BlitzY | Apocalypse | Retro | Radeon | BlitzY | Retro | Apocalypse</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xNw2qPX_jEQ</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8088,6 +8598,11 @@
           <t>BlitzY | Apocalypse | Retro | Citadel | Neo Dark Origin | BlitzY | Citadel | Neo Dark Origin | Retro</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yTwCm4gqHzg</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8134,6 +8649,11 @@
           <t>La Campanella | Apocalypse | Neo Dark Origin | Retro | Tempest | La Campanella | Retro | Apocalypse | Neo Dark Origin</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8o-zSR5a05o</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8180,6 +8700,11 @@
           <t>Retro | Neo Dark Origin | Polypoid | Apocalypse | Tempest | Apocalypse | Retro | Neo Dark Origin | Polypoid</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nX4XIwY9g8M</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8226,6 +8751,11 @@
           <t>Apocalypse | Retro | Neo Dark Origin | La Campanella | Tempest | Retro | Apocalypse | La Campanella | Tempest</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=O9zoakvWMC4</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8272,6 +8802,11 @@
           <t>Apocalypse | Neo Dark Origin | Polypoid | Tempest | Retro | Tempest | Polypoid | Neo Dark Origin | Retro</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0XqTsxb2fNU</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8318,6 +8853,11 @@
           <t>Neo Dark Origin | Retro | Invader | Apocalypse | La Campanella | Apocalypse | Invader | Retro | Neo Dark Origin</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=C3OdA4OHzCk</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8364,6 +8904,11 @@
           <t>Polypoid | Tempest | Retro | Neo Dark Origin | Invader | Invader | Neo Dark Origin | Retro | Polypoid</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=r7H2chNRSlo</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8410,6 +8955,11 @@
           <t>Tempest | Retro | Apocalypse | La Campanella | Invader | Retro | Apocalypse | Tempest | Invader</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WTxnSsfjgtc</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8456,6 +9006,11 @@
           <t>Retro | Apocalypse | Polypoid | Neo Dark Origin | Tempest | Polypoid | Apocalypse | Tempest | Neo Dark Origin</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WjQ46QMlImo</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8502,6 +9057,11 @@
           <t>Polypoid | Apocalypse | La Campanella | Tempest | Neo Dark Origin | La Campanella | Polypoid | Apocalypse | Neo Dark Origin</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uwN78ZGAiTk</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8548,6 +9108,11 @@
           <t>Polypoid | Tempest | Apocalypse | Neo Dark Origin | Retro | Apocalypse | Neo Dark Origin | Polypoid | Tempest</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OZbMpmy2f6o</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8594,6 +9159,11 @@
           <t>Tempest | Retro | Neo Dark Origin | La Campanella | Apocalypse | La Campanella | Retro | Apocalypse | Tempest</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=11BBxVOSDEg</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8732,6 +9302,11 @@
           <t>Invader | Polypoid | Apocalypse | Retro | Tempest | Invader | Apocalypse | Polypoid | Retro</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LkXFdeNUH0M</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8778,6 +9353,11 @@
           <t>Apocalypse | Retro | Tempest | La Campanella | Invader | Tempest | Retro | La Campanella | Apocalypse</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2ufNBzE_LCw</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8824,6 +9404,11 @@
           <t>Tempest | Polypoid | Retro | Apocalypse | Invader | Polypoid | Invader | Retro | Tempest</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g13NqqWR1mU</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8870,6 +9455,11 @@
           <t>Polypoid | Retro | Apocalypse | Invader | Tempest | Polypoid | Retro | Apocalypse | Invader</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BZjD6FKcF8k</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8916,6 +9506,11 @@
           <t>Polypoid | Tempest | Retro | Neo Dark Origin | Apocalypse | Tempest | Polypoid | Neo Dark Origin | Retro</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LneT-pifdFE</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8962,6 +9557,11 @@
           <t>Polypoid | Neo Dark Origin | Retro | Apocalypse | Tempest | Apocalypse | Tempest | Polypoid | Neo Dark Origin</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2Dviar2kflM</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9008,6 +9608,11 @@
           <t>Polypoid | Retro | Apocalypse | Invader | Tempest | Polypoid | Retro | Apocalypse | Invader</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VoA4FqsUsJU</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9054,6 +9659,11 @@
           <t>Tempest | Apocalypse | Polypoid | Retro | Neo Dark Origin | Tempest | Polypoid | Neo Dark Origin | Retro</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZRISZv9zz9g</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9100,6 +9710,11 @@
           <t>Retro | Polypoid | Apocalypse | Tempest | Neo Dark Origin | Retro | Polypoid | Apocalypse | Tempest</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TmeNYYss5aE</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9146,6 +9761,11 @@
           <t>Polypoid | Apocalypse | Retro | Neo Dark Origin | Tempest | Polypoid | Apocalypse | Neo Dark Origin | Tempest</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-1_-Ga8ANEQ</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9192,6 +9812,11 @@
           <t>Retro | Polypoid | Neo Dark Origin | Tempest | Apocalypse | Retro | Neo Dark Origin | Polypoid | Tempest</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=N64AkZSS02k</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9238,6 +9863,11 @@
           <t>Neo Dark Origin | Polypoid | Tempest | Apocalypse | Retro | Polypoid | Retro | Apocalypse | Tempest</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xTPhlU1jzXI</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9284,6 +9914,11 @@
           <t>Apocalypse | Polypoid | La Campanella | Invader | Retro | La Campanella | Retro | Polypoid | Invader</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7iz7gbrqkc8</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9330,6 +9965,11 @@
           <t>Neo Dark Origin | La Campanella | Apocalypse | Tempest | Retro | La Campanella | Neo Dark Origin | Apocalypse | Retro</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JnAOfGj2Sis</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9376,6 +10016,11 @@
           <t>Vermeer | Retro | Neo Sylphid | Neo Heartbreak Ridge Line | Dark Origin | Retro | Neo Heartbreak Ridge Line | Vermeer | Dark Origin</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kSCyXpromp8</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9422,6 +10067,11 @@
           <t>76 | Neo Sylphid | Retro | Neo Heartbreak Ridge Line | Nemesis | Vermeer | Dark Origin | 76 | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VwcJZOWYNwI</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9468,6 +10118,11 @@
           <t>Neo Sylphid | Neo Heartbreak Ridge Line | 76 | Nemesis | Vermeer | Dark Origin | Retro | Neo Heartbreak Ridge Line | Vermeer</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=q403kU_umf8</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9514,6 +10169,11 @@
           <t>Vermeer | Dark Origin | Neo Sylphid | Nemesis | 76 | Neo Heartbreak Ridge Line | Retro | Neo Sylphid | Vermeer</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=r4607M6XKlU</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9560,6 +10220,11 @@
           <t>Neo Heartbreak Ridge Line | Retro | Neo Sylphid | Nemesis | Vermeer | 76 | Dark Origin | Neo Sylphid | Retro</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aXl6-ZZQCJc</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9606,6 +10271,11 @@
           <t>Retro | Vermeer | Dark Origin | Neo Sylphid | Nemesis | Neo Heartbreak Ridge Line | 76 | Dark Origin | Vermeer</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=p90wUsxOZb0</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9652,6 +10322,11 @@
           <t>Vermeer | Neo Sylphid | Retro | Neo Heartbreak Ridge Line | Dark Origin | Nemesis | 76 | Neo Heartbreak Ridge Line | Dark Origin</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=b0dQcT2OVhI</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9698,6 +10373,11 @@
           <t>Retro | Nemesis | Vermeer | Neo Heartbreak Ridge Line | 76 | Dark Origin | Neo Sylphid | Nemesis | Vermeer</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hhEwYSW-nq8</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9744,6 +10424,11 @@
           <t>Nemesis | Vermeer | Neo Heartbreak Ridge Line | Neo Sylphid | Dark Origin | Retro | 76 | Vermeer | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tkhpy4OGLd0</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9790,6 +10475,11 @@
           <t>Dark Origin | Neo Heartbreak Ridge Line | Vermeer | 76 | Nemesis | Retro | Neo Sylphid | 76 | Vermeer</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=a_XzNQa8Cyk</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9836,6 +10526,11 @@
           <t>Retro | 76 | Dark Origin | Neo Sylphid | Neo Heartbreak Ridge Line | Vermeer | Nemesis | Neo Heartbreak Ridge Line | 76</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dJmfVGp8YDU</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9882,6 +10577,11 @@
           <t>Vermeer | Neo Sylphid | Retro | Neo Heartbreak Ridge Line | 76 | Nemesis | Dark Origin | Vermeer | Neo Heartbreak Ridge Line</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iHeweHA3KpI</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -9928,6 +10628,11 @@
           <t>Vermeer | Neo Heartbreak Ridge Line | Retro | Dark Origin | Neo Sylphid | Nemesis | 76 | Vermeer | Dark Origin</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GU6jnfICfJ0</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9974,6 +10679,11 @@
           <t>Vermeer | Dark Origin | Neo Sylphid | Nemesis | 76 | Neo Heartbreak Ridge Line | Retro | Vermeer | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=I4g2uzIi2sY</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10020,6 +10730,11 @@
           <t>Vermeer | Neo Sylphid | Nemesis | Dark Origin | Retro | 76 | Neo Heartbreak Ridge Line | Vermeer | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=z3a_u-m5xsM</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10066,6 +10781,11 @@
           <t>Vermeer | Neo Heartbreak Ridge Line | 76 | Neo Sylphid | Dark Origin | Nemesis | Retro | Nemesis | Neo Heartbreak Ridge Line</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wQFdYPXw5mA</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10112,6 +10832,11 @@
           <t>Neo Heartbreak Ridge Line | 76 | Vermeer | Nemesis | Retro | Neo Sylphid | Dark Origin | Vermeer | Nemesis</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=V3crGgLZX_Y</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10158,6 +10883,11 @@
           <t>Dark Origin | Neo Heartbreak Ridge Line | Vermeer | 76 | Nemesis | Retro | Neo Sylphid | 76 | Vermeer</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=E6SbuuXRI4g</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10204,6 +10934,11 @@
           <t>Retro | Vermeer | Neo Heartbreak Ridge Line | 76 | Dark Origin | Nemesis | Neo Sylphid | Nemesis | Vermeer</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A4CZyOIXGF8</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10250,6 +10985,11 @@
           <t>Nemesis | Dark Origin | Vermeer | 76 | Neo Heartbreak Ridge Line | Retro | Neo Sylphid | Vermeer | Retro</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ttkokJykXIo</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10296,6 +11036,11 @@
           <t>Vermeer | Neo Heartbreak Ridge Line | Nemesis | Dark Origin | Neo Sylphid | Retro | 76 | Vermeer | Nemesis</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uo6tTx7n8v4</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10342,6 +11087,11 @@
           <t>Retro | Vermeer | Neo Heartbreak Ridge Line | Neo Sylphid | 76 | Dark Origin | Nemesis | Vermeer | 76</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VW1QMRpgTaI</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10388,6 +11138,11 @@
           <t>Dark Origin | 76 | Neo Heartbreak Ridge Line | Retro | Vermeer | Nemesis | Neo Sylphid | Nemesis | Neo Heartbreak Ridge Line</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wTaMwHGmkE4</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10434,6 +11189,11 @@
           <t>Vermeer | Butter | Allegro | Neo Sylphid | Odyssey | Nemesis | Neo Arkanoid | Butter | Odyssey</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gAB0yS9nqyM</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10480,6 +11240,11 @@
           <t>Odyssey | Vermeer | Neo Sylphid | Butter | Nemesis | Allegro | Neo Arkanoid | Vermeer | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5FPzoJXlfok</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10526,6 +11291,11 @@
           <t>Vermeer | Odyssey | Allegro | Neo Sylphid | Neo Arkanoid | Nemesis | Butter | Odyssey | Nemesis</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ChKzx8ozBpI</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10572,6 +11342,11 @@
           <t>Butter | Neo Arkanoid | Vermeer | Allegro | Odyssey | Nemesis | Neo Sylphid | Allegro | Vermeer</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DR-c3pd2Tc0</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10618,6 +11393,11 @@
           <t>Allegro | Vermeer | Neo Arkanoid | Odyssey | Butter | Neo Sylphid | Nemesis | Odyssey | Vermeer</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=S3NNscXGbz8</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10664,6 +11444,11 @@
           <t>Vermeer | Neo Arkanoid | Allegro | Butter | Odyssey | Nemesis | Neo Sylphid | Odyssey | Vermeer</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=R3t8zu-pCh0</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -10710,6 +11495,11 @@
           <t>Allegro | Butter | Vermeer | Neo Sylphid | Neo Arkanoid | Nemesis | Odyssey | Butter | Allegro</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8rQ86GwzenE</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -10756,6 +11546,11 @@
           <t>Vermeer | Butter | Neo Sylphid | Neo Arkanoid | Nemesis | Allegro | Odyssey | Neo Arkanoid | Odyssey</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UAHA1cz_7-A</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10802,6 +11597,11 @@
           <t>Vermeer | Neo Arkanoid | Butter | Allegro | Neo Sylphid | Nemesis | Odyssey | Vermeer | Odyssey</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=huc5VPn_61k</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10848,6 +11648,11 @@
           <t>Vermeer | Odyssey | Allegro | Neo Arkanoid | Neo Sylphid | Butter | Nemesis | Vermeer | Allegro</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MYqkINIs35Y</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10894,6 +11699,11 @@
           <t>Allegro | Vermeer | Neo Sylphid | Nemesis | Butter | Odyssey | Neo Arkanoid | Allegro | Vermeer</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IUn142lEGQk</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10940,6 +11750,11 @@
           <t>Vermeer | Allegro | Butter | Neo Sylphid | Nemesis | Odyssey | Neo Arkanoid | Odyssey | Butter</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=1ZA0TrLwT1E</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10986,6 +11801,11 @@
           <t>Butter | Neo Arkanoid | Vermeer | Odyssey | Nemesis | Allegro | Neo Sylphid | Neo Arkanoid | Vermeer</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2BEGqwF_dFA</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11032,6 +11852,11 @@
           <t>Vermeer | Neo Arkanoid | Butter | Neo Sylphid | Allegro | Nemesis | Odyssey | Neo Arkanoid | Odyssey</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=s7Y3JzuvX5Y</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11078,6 +11903,11 @@
           <t>Neo Arkanoid | Butter | Allegro | Vermeer | Neo Sylphid | Nemesis | Odyssey | Neo Arkanoid | Allegro</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WN5I0cqDAmo</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11124,6 +11954,11 @@
           <t>Vermeer | Butter | Odyssey | Neo Sylphid | Allegro | Nemesis | Neo Arkanoid | Vermeer | Nemesis</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vCXSEGxXhLQ</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11170,6 +12005,11 @@
           <t>Vermeer | Butter | Odyssey | Neo Arkanoid | Allegro | Neo Sylphid | Nemesis | Vermeer | Allegro</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=znjDirLvE58</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11216,6 +12056,11 @@
           <t>Butter | Neo Sylphid | Odyssey | Vermeer | Neo Arkanoid | Allegro | Nemesis | Allegro | Vermeer</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ctb56aEcciw</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11262,6 +12107,11 @@
           <t>Neo Arkanoid | Odyssey | Vermeer | Neo Sylphid | Allegro | Butter | Nemesis | Odyssey | Vermeer</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A2atKlGGAnM</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11308,6 +12158,11 @@
           <t>Neo Sylphid | Neo Arkanoid | Allegro | Vermeer | Odyssey | Nemesis | Butter | Allegro | Vermeer</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iragZqdUGDo</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -11354,6 +12209,11 @@
           <t>Vermeer | Monopoly | Eclipse | Butter | Allegro | Revolver | Metaverse | Vermeer | Allegro</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sBm9GpCnx-k</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11400,6 +12260,11 @@
           <t>Eclipse | Allegro | Butter | Vermeer | Metaverse | Revolver | Monopoly | Eclipse | Butter</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pCPIYZrPRrc</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11441,6 +12306,11 @@
       <c r="I177" t="n">
         <v>9</v>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VeDre6RX3aY</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11487,6 +12357,11 @@
           <t>Eclipse | Vermeer | Revolver | Butter | Monopoly | Metaverse | Allegro | Vermeer | Monopoly</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lCzvszD5A5Y</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11533,6 +12408,11 @@
           <t>Allegro | Vermeer | Eclipse | Metaverse | Revolver | Butter | Monopoly | Allegro | Vermeer</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kcgNrxbiVx4</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11579,6 +12459,11 @@
           <t>Vermeer | Metaverse | Revolver | Eclipse | Butter | Monopoly | Allegro | Vermeer | Revolver</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6vQmc490V8U</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11625,6 +12510,11 @@
           <t>Eclipse | Metaverse | Monopoly | Allegro | Vermeer | Revolver | Butter | Eclipse | Revolver</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GOQtMW5nPlA</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11671,6 +12561,11 @@
           <t>Allegro | Vermeer | Eclipse | Monopoly | Butter | Revolver | Metaverse | Monopoly | Vermeer</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_FSp3LYYBtE</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11717,6 +12612,11 @@
           <t>Allegro | Eclipse | Revolver | Metaverse | Vermeer | Monopoly | Butter | Eclipse | Vermeer</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=w-55DsK6a_g</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11763,6 +12663,11 @@
           <t>Vermeer | Allegro | Revolver | Monopoly | Metaverse | Eclipse | Butter | Revolver | Monopoly</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=II5We9Kq9os</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11809,6 +12714,11 @@
           <t>Eclipse | Vermeer | Butter | Allegro | Monopoly | Revolver | Metaverse | Allegro | Vermeer</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wq3Vj_d0VPU</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11855,6 +12765,11 @@
           <t>Allegro | Butter | Eclipse | Vermeer | Metaverse | Revolver | Monopoly | Eclipse | Revolver</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x-UZ_pfATiM</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11901,6 +12816,11 @@
           <t>Allegro | Revolver | Metaverse | Eclipse | Vermeer | Monopoly | Butter | Revolver | Eclipse</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=40sYqWlUy2I</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11947,6 +12867,11 @@
           <t>Eclipse | Butter | Monopoly | Vermeer | Revolver | Allegro | Metaverse | Vermeer | Allegro</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Xra54j-RFdw</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11993,6 +12918,11 @@
           <t>Eclipse | Allegro | Monopoly | Vermeer | Butter | Revolver | Metaverse | Vermeer | Metaverse</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qh7cNgc51Qo</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -12039,6 +12969,11 @@
           <t>Allegro | Eclipse | Vermeer | Monopoly | Revolver | Butter | Metaverse | Eclipse | Butter</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lT6L8CFLyxY</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -12085,6 +13020,11 @@
           <t>Allegro | Metaverse | Butter | Monopoly | Vermeer | Revolver | Eclipse | Butter | Allegro</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OpkLDX69pbs</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -12131,6 +13071,11 @@
           <t>Eclipse | Monopoly | Metaverse | Revolver | Vermeer | Butter | Allegro | Eclipse | Monopoly</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x2SpXOJmABs</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -12177,6 +13122,11 @@
           <t>Revolver | Monopoly | Allegro | Vermeer | Butter | Eclipse | Metaverse | Eclipse | Butter</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iwKzgDuotb8</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -12223,6 +13173,11 @@
           <t>Vermeer | Eclipse | Revolver | Metaverse | Butter | Monopoly | Allegro | Metaverse | Vermeer</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_gmFMxExRXo</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -12269,6 +13224,11 @@
           <t>Polypoid | Revolver | Neo Sylphid | Ascension | Allegro | Eclipse | Fighting Spirit | Revolver | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=h-xhkfGSGUM</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12315,6 +13275,11 @@
           <t>Fighting Spirit | Revolver | Polypoid | Allegro | Neo Sylphid | Eclipse | Ascension | Eclipse | Fighting Spirit</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0q1QSVGiO9w</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12361,6 +13326,11 @@
           <t>Neo Sylphid | Revolver | Ascension | Fighting Spirit | Allegro | Polypoid | Eclipse | Neo Sylphid | Polypoid</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TAUBYa_FBPs</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -12453,6 +13423,11 @@
           <t>Polypoid | Fighting Spirit | Neo Sylphid | Ascension | Eclipse | Revolver | Allegro | Polypoid | Allegro</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RwU27zrMFDU</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12499,6 +13474,11 @@
           <t>Ascension | Neo Sylphid | Fighting Spirit | Revolver | Polypoid | Eclipse | Allegro | Polypoid | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Ik5FlpP8SFg</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12591,6 +13571,11 @@
           <t>Fighting Spirit | Polypoid | Neo Sylphid | Allegro | Revolver | Ascension | Eclipse | Eclipse | Polypoid</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SXrFwKlw904</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12637,6 +13622,11 @@
           <t>Allegro | Vermeer | Neo Arkanoid | Odyssey | Butter | Neo Sylphid | Nemesis | Odyssey | Nemesis</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=WYdlsWHin7I</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12683,6 +13673,11 @@
           <t>Ascension | Polypoid | Eclipse | Allegro | Lemon | Good Night | Revolver | Revolver | Good Night</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=R6OyrTHPrLY</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12729,6 +13724,11 @@
           <t>Eclipse | Good Night | Ascension | Lemon | Revolver | Largo | Polypoid | Revolver | Largo</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W9s5gRss1e8</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12775,6 +13775,11 @@
           <t>Good Night | Polypoid | Largo | Ascension | Eclipse | Lemon | Revolver | Good Night | Ascension</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MPNLAgHFTh0</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12821,6 +13826,11 @@
           <t>Ascension | Polypoid | Revolver | Lemon | Largo | Eclipse | Good Night | Revolver | Ascension</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_-j6VhnUzSM</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12867,6 +13877,11 @@
           <t>Polypoid | Eclipse | Revolver | Good Night | Lemon | Ascension | Largo | Revolver | Polypoid</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=v6sHt_GAYCY</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12913,6 +13928,11 @@
           <t>Polypoid | Ascension | Eclipse | Largo | Revolver | Lemon | Good Night | Revolver | Ascension</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vpPR-KG5wEs</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12959,6 +13979,11 @@
           <t>Ascension | Polypoid | Revolver | Eclipse | Largo | Good Night | Lemon | Polypoid | Ascension</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6yIEItwyXZM</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -13005,6 +14030,11 @@
           <t>Revolver | Ascension | Largo | Lemon | Good Night | Eclipse | Polypoid | Ascension | Largo</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aeaNgOwfQ-Q</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -13051,6 +14081,11 @@
           <t>Largo | Eclipse | Good Night | Ascension | Polypoid | Lemon | Revolver | Largo | Good Night</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kMqiK5y0mOA</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13097,6 +14132,11 @@
           <t>Largo | Polypoid | Ascension | Eclipse | Lemon | Good Night | Revolver | Largo | Good Night</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GYLNplc8kN4</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -13143,6 +14183,11 @@
           <t>Eclipse | Largo | Ascension | Good Night | Polypoid | Revolver | Lemon | Polypoid | Ascension</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ztpafy4sVa8</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13189,6 +14234,11 @@
           <t>Good Night | Largo | Eclipse | Revolver | Polypoid | Lemon | Ascension | Good Night | Eclipse</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=kQTNyTnGzOY</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13235,6 +14285,11 @@
           <t>Polypoid | Ascension | Eclipse | Ultimate Stream | Fighting Spirit | Hidden Track | Polaris Rhapsody | Ascension | Ultimate Stream</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SVJjZyqAwNc</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13281,6 +14336,11 @@
           <t>Polypoid | Ascension | Fighting Spirit | Hidden Track | Eclipse | Ultimate Stream | Polaris Rhapsody | Polypoid | Fighting Spirit</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=r3URcAlvGJo</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13327,6 +14387,11 @@
           <t>Ascension | Ultimate Stream | Fighting Spirit | Polypoid | Eclipse | Hidden Track | Polaris Rhapsody | Ascension | Polypoid</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=02vjRw70NBk</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13373,6 +14438,11 @@
           <t>Polaris Rhapsody | Polypoid | Ultimate Stream | Ascension | Eclipse | Hidden Track | Fighting Spirit | Eclipse | Polypoid</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=5nUXPPZMWFU</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13419,6 +14489,11 @@
           <t>Ultimate Stream | Fighting Spirit | Eclipse | Polypoid | Ascension | Polaris Rhapsody | Hidden Track | Ultimate Stream | Fighting Spirit</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NUTIg6kPqW8</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13465,6 +14540,11 @@
           <t>Ascension | Polaris Rhapsody | Eclipse | Fighting Spirit | Ultimate Stream | Polypoid | Hidden Track | Polypoid | Polaris Rhapsody</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=pj-LMZmKKts</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13511,6 +14591,11 @@
           <t>Polypoid | Polaris Rhapsody | Ultimate Stream | Fighting Spirit | Hidden Track | Eclipse | Ascension | Ultimate Stream | Fighting Spirit</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OxtSZF_L9X4</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13557,6 +14642,11 @@
           <t>Fighting Spirit | Ultimate Stream | Polypoid | Ascension | Hidden Track | Polaris Rhapsody | Eclipse | Ultimate Stream | Fighting Spirit</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ADgXuNzjbY8</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13603,6 +14693,11 @@
           <t>Hidden Track | Polypoid | Polaris Rhapsody | Ascension | Eclipse | Ultimate Stream | Fighting Spirit | Ascension | Fighting Spirit</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-7KefhieanU</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13649,6 +14744,11 @@
           <t>Fighting Spirit | Ascension | Hidden Track | Ultimate Stream | Eclipse | Polypoid | Polaris Rhapsody | Ultimate Stream | Hidden Track</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=SaWgtKjaDso</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13695,6 +14795,11 @@
           <t>Ultimate Stream | Fighting Spirit | Eclipse | Hidden Track | Ascension | Polypoid | Polaris Rhapsody | Fighting Spirit | Ultimate Stream</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=47gNZPKnxnU</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13741,6 +14846,11 @@
           <t>Polypoid | Hidden Track | Eclipse | Ultimate Stream | Fighting Spirit | Polaris Rhapsody | Ascension | Eclipse | Ultimate Stream</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UY7UZwqfBGs</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13787,6 +14897,11 @@
           <t>Hidden Track | Polypoid | Polaris Rhapsody | Ultimate Stream | Ascension | Fighting Spirit | Eclipse | Fighting Spirit | Polaris Rhapsody</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IVSBMWNzBn8</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13833,6 +14948,11 @@
           <t>Hidden Track | Polypoid | Ultimate Stream | Fighting Spirit | Polaris Rhapsody | Eclipse | Ascension | Ultimate Stream | Polypoid</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=m5yd2wgxOsM</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13879,6 +14999,11 @@
           <t>Eclipse | Polypoid | Hidden Track | Polaris Rhapsody | Ultimate Stream | Ascension | Fighting Spirit | Polypoid | Eclipse</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YFzijCaNs4g</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13925,6 +15050,11 @@
           <t>Ascension | Polypoid | Eclipse | Fighting Spirit | Hidden Track | Polaris Rhapsody | Ultimate Stream | Ultimate Stream | Polaris Rhapsody</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=sEPfTapPW2Q</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13971,6 +15101,11 @@
           <t>Eclipse | Polypoid | Fighting Spirit | Ascension | Hidden Track | Ultimate Stream | Polaris Rhapsody | Eclipse | Fighting Spirit</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hlL0RX_EHrg</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14017,6 +15152,11 @@
           <t>Ultimate Stream | Ascension | Polypoid | Fighting Spirit | Polaris Rhapsody | Eclipse | Hidden Track | Polypoid | Hidden Track</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=62eMUiT_AkI</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14063,6 +15203,11 @@
           <t>Fighting Spirit | Polaris Rhapsody | Polypoid | Eclipse | Ultimate Stream | Ascension | Hidden Track | Polypoid | Polaris Rhapsody</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tEjNqjmdepw</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14109,6 +15254,11 @@
           <t>Fighting Spirit | Ultimate Stream | Polypoid | Eclipse | Hidden Track | Ascension | Polaris Rhapsody | Polypoid | Ascension</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zkecPlmUiAA</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14155,6 +15305,11 @@
           <t>Polypoid | Ringing Bloom SE | Shakuras Temple | Eclipse | Benzene | Polypoid | Benzene | Eclipse | Ringing Bloom SE</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IeoNeNfoPAk</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14201,6 +15356,11 @@
           <t>Polypoid | Shakuras Temple | Ringing Bloom SE | Eclipse | Benzene | Shakuras Temple | Eclipse | Polypoid | Ringing Bloom SE</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=g8F3dlb1fqY</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14247,6 +15407,11 @@
           <t>Eclipse | Polypoid | Shakuras Temple | Ringing Bloom SE | Benzene | Benzene | Ringing Bloom SE | Eclipse | Shakuras Temple</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=vrAkM34Ahn0</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14293,6 +15458,11 @@
           <t>Ringing Bloom SE | Polypoid | Shakuras Temple | Optimizer | Plasma | Eclipse | Benzene | Polypoid | Ringing Bloom SE</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eslev1CEWVw</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14339,6 +15509,11 @@
           <t>Polypoid | Ringing Bloom SE | Benzene | Plasma | Optimizer | Eclipse | Shakuras Temple | Plasma | Ringing Bloom SE</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6NsFkHCc7Jg</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14385,6 +15560,11 @@
           <t>Plasma | Ringing Bloom SE | Shakuras Temple | Benzene | Optimizer | Polypoid | Eclipse | Plasma | Eclipse</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4EULsJ-y9d0</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14431,6 +15611,11 @@
           <t>Shakuras Temple | Polypoid | Ringing Bloom SE | Benzene | Plasma | Optimizer | Eclipse | Shakuras Temple | Polypoid</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RkdIbZq4hsg</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14477,6 +15662,11 @@
           <t>Shakuras Temple | Polypoid | Plasma | Optimizer | Polypoid | Benzene | Eclipse | Ringing Bloom | Plasma</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vx8kM-ExkhE</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14523,6 +15713,11 @@
           <t>Plasma | Eclipse | Polypoid | Shakuras Temple | Benzene | Ringing Bloom | Optimizer | Plasma | Polypoid</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=JCTp-a4NVKU</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14569,6 +15764,11 @@
           <t>Plasma | Benzene | Ringing Bloom | Polypoid | Eclipse | Optimizer | Shakuras Temple | Plasma | Polypoid</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=l6CcoRI5WVk</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14615,6 +15815,11 @@
           <t>Benzene | Ringing Bloom | Plasma | Optimizer | Polypoid | Shakuras Temple | Eclipse | Plasma | Ringing Bloom</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=DdvCoMZtqd8</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14661,6 +15866,11 @@
           <t>Ringing Bloom | Benzene | Eclipse | Plasma | Optimizer | Polypoid | Shakuras Temple | Polypoid | Plasma</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9OTNyF8kH4w</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14707,6 +15917,11 @@
           <t>Benzene | Polypoid | Eclipse | Shakuras Temple | Optimizer | Plasma | Ringing Bloom | Benzene | Polypoid</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wa0X_L8h8oM</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14753,6 +15968,11 @@
           <t>Polypoid | Plasma | Optimizer | Ringing Bloom | Eclipse | Shakuras Temple | Benzene | Polypoid | Shakuras Temple</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UT9QszTBJvk</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14799,6 +16019,11 @@
           <t>Polypoid | Ringing Bloom | Shakuras Temple | Optimizer | Plasma | Benzene | Eclipse | Plasma | Ringing Bloom</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yHfn-SvnYds</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14845,6 +16070,11 @@
           <t>Optimizer | Benzene | Ringing Bloom | Shakuras Temple | Plasma | Polypoid | Eclipse | Benzene | Optimizer</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lZaoh1b5gfk</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14891,6 +16121,11 @@
           <t>Polypoid | Ringing Bloom | Eclipse | Plasma | benzene | Shakuras Temple | Optimizer | Eclipse | Ringing Bloom</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=a5WWcf7MTfo</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14937,6 +16172,11 @@
           <t>Ringing Bloom | Plasma | Polypoid | Benzene | Optimizer | Eclipse | Shakuras Temple | Benzene | Ringing Bloom</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9QrRWvF9H-M</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -14983,6 +16223,11 @@
           <t>Match Point | Circuit Breakers | La Mancha | Fighting Spirit | Hitchhiker | New Bloody Ridge | Escalade | Neo Sylphid | Polypoid</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=d2lZkWki4g0</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -15029,6 +16274,11 @@
           <t>La Mancha | Escalade | Horizon Lunar Colony | Fighting Spirit | Polypoid | Neo Sylphid | Circuit Breakers | New Bloody Ridge | Match Point</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=MJpVscyKYEk</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15075,6 +16325,11 @@
           <t>Circuit Breakers | Escalade | Polypoid | Hitchhiker | Neo Sylphid | Horizon Lunar Colony | la mancha | Match Point | New Bloody Ridge</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NWu4TfDciTE</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15116,6 +16371,11 @@
       <c r="I257" t="n">
         <v>9</v>
       </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qZ2Eq8TEzLM</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15162,6 +16422,11 @@
           <t>Fighting Spirit | Neo Sylphid | Polypoid | Hitchhiker | La Mancha | Circuit Breakers | Horizon Lunar Colony | Match Point | New Bloody Ridge</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iQbvsWJ6Cgs</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15208,6 +16473,11 @@
           <t>Hitchhiker | Fighting Spirit | Circuit Breakers | Neo Sylphid | Match Point | New Bloody Ridge | Polypoid | La Mancha | Escalade</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7pI-a1N1h4w</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -15254,6 +16524,11 @@
           <t>La Mancha | Fighting Spirit | New Bloody Ridge | Escalade | Circuit Breakers | Polypoid | Hitchhiker | Neo Sylphid | Horizon Lunar Colony</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=AKlWWz7BwHQ</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15300,6 +16575,11 @@
           <t>Escalade | Neo Sylphid | La Mancha | Polypoid | Hitchhiker | Horizon Lunar Colony | Match Point | Fighting Spirit | Circuit Breakers</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2N7oueo7R8E</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15346,6 +16626,11 @@
           <t>Neo Sylphid | Circuit Breakers | Match Point | Hitchhiker | Fighting Spirit | Horizon Lunar Colony | La Mancha | Polypoid | Escalade</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yI07_vQSFUQ</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15392,6 +16677,11 @@
           <t>Circuit Breakers | Fighting Spirit | La Mancha | Hitchhiker | Match Point | New Bloody Ridge | Neo Sylphid | Horizon Lunar Colony | Polypoid</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=TJcY5uCN-c0</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -15438,6 +16728,11 @@
           <t>Escalade | New Bloody Ridge | Hitchhiker | Fighting Spirit | Circuit Breakers | Polypoid | Horizon Lunar Colony | Match Point | Neo Sylphid</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=aB4nx6VTQNY</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -15484,6 +16779,11 @@
           <t>Fighting Spirit | Horizon Lunar Colony | Neo Sylphid | New Bloody Ridge | Match Point | Hitchhiker | La Mancha | Circuit Breakers | Polypoid</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=O1BXE3i06H4</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15530,6 +16830,11 @@
           <t>Fighting Spirit | Escalade | Hitchhiker | Match Point | La Mancha | Neo Sylphid | Circuit Breakers | Horizon Lunar Colony | Polypoid</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=t4TDUEcWn6w</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15576,6 +16881,11 @@
           <t>Fighting Spirit | Neo Sylphid | Match Point | Autobahn | Circuit Breakers | Polypoid | La Mancha | Escalade | New Bloody Ridge</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7MYj2Vq-FJs</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -15622,6 +16932,11 @@
           <t>Match Point | Hitchhiker | Fighting Spirit | Horizon Lunar Colony | La Mancha | Neo Sylphid | Circuit Breakers | Escalade | New Bloody Ridge</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Fanqz4ieYBw</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15668,6 +16983,11 @@
           <t>Hitchhiker | Polypoid | Match Point | La Mancha | Escalade | Neo Sylphid | Fighting Spirit | Circuit Breakers | New Bloody Ridge</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=GQjGOjCw2yk</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15714,6 +17034,11 @@
           <t>Circuit Breakers | Horizon Lunar Colony | Whiteout | Escalade | Polypoid | Match Point | Hitchhiker | Fighting Spirit | Gladiator</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Wkc_C0cNIy0</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15760,6 +17085,11 @@
           <t>Destination | Escalade | New Heartbreak Ridge | Match Point | Horizon Lunar Colony | Autobahn | Neo Sylphid | Polypoid | Whiteout</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lT23c28ZwLA</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -15806,6 +17136,11 @@
           <t>La Mancha | Destination | Overwatch | Whiteout | Circuit Breakers | Eye of the Storm | Neo Sylphid | Fighting Spirit | Gladiator</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=PG4VG-g2Fn8</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -15852,6 +17187,11 @@
           <t>Circuit Breakers | Destination | Fighting Spirit | Overwatch | Neo Sylphid | Eye of the Storm | La Mancha | New Heartbreak Ridge | Whiteout</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=fEfKPExFmG8</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -15898,6 +17238,11 @@
           <t>Overwatch | Destination | New Heartbreak Ridge | Eye of the Storm | Whiteout | La Mancha | Fighting Spirit | Neo Sylphid | Circuit Breakers</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ks3IdbX7vac</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15944,6 +17289,11 @@
           <t>Overwatch | New Heartbreak Ridge | Destination | Whiteout | Eye of the Storm | La Mancha | Fighting Spirit | Neo Sylphid | Circuit Breakers</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=0waqeDXiTrQ</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -15990,6 +17340,11 @@
           <t>New Heartbreak Ridge | Fighting Spirit | Gladiator | Overwatch | La Mancha | Circuit Breakers | Neo Sylphid | Destination | Whiteout</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=IMmQtBbPhxo</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -16036,6 +17391,11 @@
           <t>Fighting Spirit | Destination | Neo Sylphid | Circuit Breakers | Overwatch | Eye of the Storm | La Mancha | Whiteout | Gladiator</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wXSp8-vXIbQ</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -16082,6 +17442,11 @@
           <t>New Heartbreak Ridge | Neo Sylphid | Circuit Breakers | Whiteout | La Mancha | Eye of the Storm | Fighting Spirit | Overwatch | Gladiator</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ObBDilk_QSI</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16128,6 +17493,11 @@
           <t>Block Chain SE | Circuit Breakers | Overwatch | Neo Sylphid | Gladiator | New Bloody Ridge | Fighting Spirit | Tres Pass | Power Bond</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ccW3gT0QJhc</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -16174,6 +17544,11 @@
           <t>Circuit Breakers | Overwatch | Block Chain SE | Gladiator | Neo Sylphid | New Bloody Ridge | Tres Pass | Power Bond | Fighting Spirit</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rddbps0L-E0</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -16215,6 +17590,11 @@
       <c r="I281" t="n">
         <v>9</v>
       </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=4PdaCOtqKrY</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -16261,6 +17641,11 @@
           <t>Circuit Breakers | Overwatch | Power Bond | Neo Sylphid | Fighting Spirit | Tres Pass | Gladiator | Block Chain SE | New Bloody Ridge</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BzLqjhFaQdc</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -16307,6 +17692,11 @@
           <t>Overwatch | Block Chain SE | Neo Sylphid | Fighting Spirit | Circuit Breakers | Gladiator | Tres Pass | New Bloody Ridge | Power Bond</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=hPMyvpnjXBg</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16353,6 +17743,11 @@
           <t>Neo Sylphid | Fighting Spirit | Circuit Breakers | Gladiator | Power Bond | Block Chain SE | Overwatch | Tres Pass | New Bloody Ridge</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=A6We6JGmVIc</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -16399,6 +17794,11 @@
           <t>Neo Sylphid | Power Bond | Overwatch | Circuit Breakers | Fighting Spirit | Block Chain SE | New Bloody Ridge | Gladiator | Tres Pass</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zRC5VjcWjkA</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -16445,6 +17845,11 @@
           <t>Tres Pass | Overwatch | New Bloody Ridge | Fighting Spirit | Neo Sylphid | Gladiator | Block Chain SE | Circuit Breakers | Power Bond</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=bH5GXEsrrvk</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -16491,6 +17896,11 @@
           <t>Power Bond | Fighting Spirit | Overwatch | Block Chain SE | New Bloody Ridge | Gladiator | Circuit Breakers | Neo Sylphid | Tres Pass</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=imMYOHNnlf4</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16532,6 +17942,11 @@
       <c r="I288" t="n">
         <v>9</v>
       </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=gBIiIaW_uG0</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -16578,6 +17993,11 @@
           <t>New Bloody Ridge | Neo sylphid | Overwatch | Block Chain SE | Power Bond | Circuit Breakers | Gladiator | Tres Pass | Fighting Spirit</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=2dT4U1xU6Hg</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -16624,6 +18044,11 @@
           <t>Fighting Spirit | Block Chain SE | Power Bond | Overwatch | Gladiator | New Bloody Ridge | Tres Pass | Neo Sylphid | Circuit Breakers</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mzAKn2ucKR8</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -16670,6 +18095,11 @@
           <t>Circuit Breakers | Fighting Spirit | Overwatch | Neo Ground Zero | Colosseum 2 | Neo Medusa | Cross Game | Circuit Breakers | Cross Game</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=VCMKSMOTHME</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -16716,6 +18146,11 @@
           <t>Cross Game | Fighting Spirit | Overwatch | Neo Ground Zero | Neo Medusa | Circuit Breakers | Colosseum 2 | Neo Ground Zero | Circuit Breakers</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Xvv0Ghi9f1k</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -16762,6 +18197,11 @@
           <t>Overwatch | Circuit Breakers | Fighting Spirit | Colosseum 2 | Cross Game | Neo Medusa | Neo Ground Zero | Overwatch | Circuit Breakers</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=oL3iDMeq5z8</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -16808,6 +18248,11 @@
           <t>Neo Ground Zero | Fighting Spirit | Circuit Breakers | Neo Medusa | Overwatch | Colosseum 2 | Cross Game | Fighting Spirit | Neo Medusa</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BpiMbj_B2Qo</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16854,6 +18299,11 @@
           <t>Colosseum 2 | Cross Game | Circuit Breakers | Overwatch | Neo Ground Zero | Fighting Spirit | Neo Medusa | Circuit Breakers | Neo Medusa</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=FDYe2BKNV4M</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -16900,6 +18350,11 @@
           <t>Neo Medusa | Fighting Spirit | Overwatch | Circuit Breakers | Colosseum 2 | Cross Game | Neo Ground Zero | Neo Medusa | Overwatch</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=le9kBoU07zk</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -16944,6 +18399,11 @@
       <c r="J297" t="inlineStr">
         <is>
           <t>Fighting Spirit | Circuit Breakers | Neo Medusa | Colosseum 2 | Neo Ground Zero | Overwatch | Cross Game | Fighting Spirit | Circuit Breakers</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ZIYapNrkHf0</t>
         </is>
       </c>
     </row>

--- a/xlsx/sc-endgame.xlsx
+++ b/xlsx/sc-endgame.xlsx
@@ -3088,6 +3088,11 @@
           <t>Backrooms | Attitude | KnockOut | Octagon | Aiolos | Octagon | Attitude | KnockOut | Backrooms</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=i7iR6MRNgCI</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3134,6 +3139,11 @@
           <t>Colorless Fate | Aiolos | Attitude | KnockOut | Octagon | Attitude | Aiolos | Octagon | Colorless Fate</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=HjV969bqE3k</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3178,6 +3188,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>Octagon | KnockOut | Attitude | Backrooms | Aiolos | Octagon | Attitude | KnockOut | Backrooms</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ig5uN9L82zI</t>
         </is>
       </c>
     </row>
